--- a/Ecommerce_Orders_2025.xlsx
+++ b/Ecommerce_Orders_2025.xlsx
@@ -8,26 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/922af556b0391340/Desktop/Excel for data analyt/Ecommerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="11_F25DC773A252ABDACC104821515E5DF85BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93BABA71-C7E1-4CB9-B1FF-3A5FC70E9F38}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="11_F25DC773A252ABDACC104821515E5DF85BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D40D06EF-9BD0-4408-BDAD-9A9ECB696018}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3576" yWindow="4068" windowWidth="17280" windowHeight="8172" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
-    <sheet name="Funnel_Data" sheetId="3" r:id="rId2"/>
-    <sheet name="Customer_Segmentation" sheetId="4" r:id="rId3"/>
-    <sheet name="Day12_Analysis" sheetId="2" r:id="rId4"/>
+    <sheet name="Inventory_Data" sheetId="6" r:id="rId2"/>
+    <sheet name="Day12_Analysis" sheetId="2" r:id="rId3"/>
+    <sheet name="AB_Test_Data" sheetId="5" r:id="rId4"/>
+    <sheet name="Funnel_Data" sheetId="3" r:id="rId5"/>
+    <sheet name="Customer_Segmentation" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v2.0" hidden="1">Funnel_Data!$I$1:$I$3</definedName>
     <definedName name="_xlchart.v2.1" hidden="1">Funnel_Data!$J$1:$J$3</definedName>
-    <definedName name="ExternalData_1" localSheetId="2" hidden="1">Customer_Segmentation!$A$1:$H$502</definedName>
-    <definedName name="ExternalData_2" localSheetId="2" hidden="1">Customer_Segmentation!$L$1:$N$46</definedName>
+    <definedName name="ExternalData_1" localSheetId="5" hidden="1">Customer_Segmentation!$A$1:$H$502</definedName>
+    <definedName name="ExternalData_2" localSheetId="5" hidden="1">Customer_Segmentation!$L$1:$N$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="21" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6563" uniqueCount="2042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="2055">
   <si>
     <t>Order ID</t>
   </si>
@@ -6190,6 +6192,45 @@
   </si>
   <si>
     <t>High-Value</t>
+  </si>
+  <si>
+    <t>Group B Visits (Free Shipping)</t>
+  </si>
+  <si>
+    <t>Group A Vsits (Dsicounts)</t>
+  </si>
+  <si>
+    <t>Group A Purchases</t>
+  </si>
+  <si>
+    <t>Group B Purchases</t>
+  </si>
+  <si>
+    <t>Group B Conversion %</t>
+  </si>
+  <si>
+    <t>Group A Conversion %</t>
+  </si>
+  <si>
+    <t>Avg Group A Conversion</t>
+  </si>
+  <si>
+    <t>Avg Group B Conversion</t>
+  </si>
+  <si>
+    <t>Free Shipping (Group B) has a higher conversion rate (3%) than Discount (Group A, ~2.5%)—suggests customers prefer free shipping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Name </t>
+  </si>
+  <si>
+    <t>Units Sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg Stock Level </t>
+  </si>
+  <si>
+    <t>Turnover</t>
   </si>
 </sst>
 </file>
@@ -6234,7 +6275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6245,7 +6286,6 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6274,402 +6314,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Ecommerce_Orders_2025.xlsx]Customer_Segmentation!PivotTable5</c:name>
-    <c:fmtId val="1"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Customer_Segmentation!$S$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Customer_Segmentation!$R$2:$R$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>At-Risk</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Engaged</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>High-Value</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Customer_Segmentation!$S$2:$S$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>249</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>125</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>127</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F19E-4567-880C-0AED8F9923A4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1503333423"/>
-        <c:axId val="1503330543"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1503333423"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1503330543"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1503330543"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1503333423"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7065,7 +6709,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7413,7 +7057,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7821,6 +7465,692 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>A/B Test Conversion Rates</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>AB_Test_Data!$I$1:$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Avg Group A Conversion</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Avg Group B Conversion</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>AB_Test_Data!$I$2:$J$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.4283333333333328</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3328-4AB0-AAB3-BB9D03F497A6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="7121887"/>
+        <c:axId val="7119007"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="7121887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="7119007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="7119007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="7121887"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Ecommerce_Orders_2025.xlsx]Customer_Segmentation!PivotTable5</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Customer_Segmentation!$S$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Customer_Segmentation!$R$2:$R$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>At-Risk</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Engaged</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>High-Value</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Customer_Segmentation!$S$2:$S$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>127</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F19E-4567-880C-0AED8F9923A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1503333423"/>
+        <c:axId val="1503330543"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1503333423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1503330543"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1503330543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1503333423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -8088,515 +8418,47 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8759,6 +8621,525 @@
       <cs:styleClr val="auto"/>
     </cs:lnRef>
     <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -9607,7 +9988,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9664,7 +10045,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -9715,13 +10096,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -9732,19 +10106,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -9782,7 +10149,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -10126,6 +10493,514 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10634,130 +11509,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1751202</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>134923</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>6323202</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>151701</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Chart 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5731CBF-1A5A-3444-73EF-4D323B3776BF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7329042" y="866443"/>
-              <a:ext cx="4572000" cy="2759978"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This chart isn't available in your version of Excel.
-Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C43B7969-8541-2C65-1EBF-C76512539C61}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
@@ -10859,6 +11610,171 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1884A07-4D5B-ABAD-06D8-184C585290B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1751202</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>134923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>6323202</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>151701</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5731CBF-1A5A-3444-73EF-4D323B3776BF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7329042" y="866443"/>
+              <a:ext cx="4572000" cy="2759978"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>148590</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C43B7969-8541-2C65-1EBF-C76512539C61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -26057,135 +26973,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EF00804-351A-4BC4-AC10-4B5E10F53289}" name="PivotTable5" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
-  <location ref="R1:S4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="1">
-    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Segment" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EF887AA9-EC22-4036-946E-9FCBB31B23A5}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Sales By Category">
-  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of  Total Sales" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43A93027-1E21-4FD7-B066-82E2E79C3B91}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Top 5 products">
   <location ref="G5:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -26291,7 +27078,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FBF9748-6DB2-4FCC-AEB0-759B76C8B5C8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Sales By Segment">
   <location ref="D5:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -26968,6 +27755,135 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EF887AA9-EC22-4036-946E-9FCBB31B23A5}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Sales By Category">
+  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of  Total Sales" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EF00804-351A-4BC4-AC10-4B5E10F53289}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
+  <location ref="R1:S4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Segment" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="4" xr16:uid="{59F37590-95CD-4519-87C7-D229B42863A5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
@@ -67350,6 +68266,694 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EDA9D39-AB72-4AEF-BECB-94EB0CD9E2EE}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B2">
+        <f>SUMIF(Orders!$G$2:$G$1001,A2,Orders!$H$2:$H$1001)</f>
+        <v>313</v>
+      </c>
+      <c r="C2">
+        <f>ROUND(B2/9*2.5,0)</f>
+        <v>87</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3.5977011490000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B3">
+        <f>SUMIF(Orders!$G$2:$G$1001,A3,Orders!$H$2:$H$1001)</f>
+        <v>305</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C7" si="0">ROUND(B3/9*2.5,0)</f>
+        <v>85</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.588235294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B4">
+        <f>SUMIF(Orders!$G$2:$G$1001,A4,Orders!$H$2:$H$1001)</f>
+        <v>393</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.605504587</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B5">
+        <f>SUMIF(Orders!$G$2:$G$1001,A5,Orders!$H$2:$H$1001)</f>
+        <v>387</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.5833333330000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B6">
+        <f>SUMIF(Orders!$G$2:$G$1001,A6,Orders!$H$2:$H$1001)</f>
+        <v>310</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.6046511630000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B7">
+        <f>SUMIF(Orders!$G$2:$G$1001,A7,Orders!$H$2:$H$1001)</f>
+        <v>351</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.5816326530000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA538C55-3497-42D2-A195-3A2123A31A61}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <f>SUM(Orders!J2:J1001)</f>
+        <v>594986</v>
+      </c>
+      <c r="B2">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="2">
+        <f>A2/B2</f>
+        <v>594.98599999999999</v>
+      </c>
+      <c r="D2">
+        <f>COUNTA(_xlfn.UNIQUE(Orders!C2:C1001))</f>
+        <v>501</v>
+      </c>
+      <c r="E2">
+        <f>COUNTIF(Orders!K2:K1001,"&gt;1")</f>
+        <v>499</v>
+      </c>
+      <c r="F2" s="3">
+        <f>E2/D2*100</f>
+        <v>99.600798403193608</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2012</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>2015</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B6">
+        <v>30008</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E6">
+        <v>312714</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>1995</v>
+      </c>
+      <c r="H6">
+        <v>141154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B7">
+        <v>359997</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E7">
+        <v>282272</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H7">
+        <v>114051</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B8">
+        <v>204981</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E8">
+        <v>594986</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H8">
+        <v>104792</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B9">
+        <v>594986</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="H9">
+        <v>74774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="H10">
+        <v>70291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="5" t="s">
+        <v>2011</v>
+      </c>
+      <c r="H11">
+        <v>505062</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4E2C0D-628C-4D03-AADB-F392E4F79741}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="9" max="10" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="108.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2049</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B2">
+        <v>5000</v>
+      </c>
+      <c r="C2">
+        <v>114</v>
+      </c>
+      <c r="D2">
+        <v>5000</v>
+      </c>
+      <c r="E2">
+        <v>142</v>
+      </c>
+      <c r="F2">
+        <f>C2/B2*100</f>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="G2">
+        <f>E2/D2*100</f>
+        <v>2.8400000000000003</v>
+      </c>
+      <c r="I2" s="3">
+        <f>AVERAGE(F2:F13)</f>
+        <v>2.4283333333333328</v>
+      </c>
+      <c r="J2" s="3">
+        <f>AVERAGE(G2:G13)</f>
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>45323</v>
+      </c>
+      <c r="B3">
+        <v>5000</v>
+      </c>
+      <c r="C3">
+        <v>117</v>
+      </c>
+      <c r="D3">
+        <v>5000</v>
+      </c>
+      <c r="E3">
+        <v>144</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F13" si="0">C3/B3*100</f>
+        <v>2.34</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G13" si="1">E3/D3*100</f>
+        <v>2.88</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>45352</v>
+      </c>
+      <c r="B4">
+        <v>5000</v>
+      </c>
+      <c r="C4">
+        <v>112</v>
+      </c>
+      <c r="D4">
+        <v>5000</v>
+      </c>
+      <c r="E4">
+        <v>144</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>2.2399999999999998</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>2.88</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B5">
+        <v>5000</v>
+      </c>
+      <c r="C5">
+        <v>138</v>
+      </c>
+      <c r="D5">
+        <v>5000</v>
+      </c>
+      <c r="E5">
+        <v>158</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>2.76</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>3.16</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>45413</v>
+      </c>
+      <c r="B6">
+        <v>5000</v>
+      </c>
+      <c r="C6">
+        <v>139</v>
+      </c>
+      <c r="D6">
+        <v>5000</v>
+      </c>
+      <c r="E6">
+        <v>158</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>2.78</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>3.16</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>45444</v>
+      </c>
+      <c r="B7">
+        <v>5000</v>
+      </c>
+      <c r="C7">
+        <v>129</v>
+      </c>
+      <c r="D7">
+        <v>5000</v>
+      </c>
+      <c r="E7">
+        <v>152</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>2.58</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>3.04</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B8">
+        <v>5000</v>
+      </c>
+      <c r="C8">
+        <v>130</v>
+      </c>
+      <c r="D8">
+        <v>5000</v>
+      </c>
+      <c r="E8">
+        <v>147</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>2.6</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>2.94</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B9">
+        <v>5000</v>
+      </c>
+      <c r="C9">
+        <v>128</v>
+      </c>
+      <c r="D9">
+        <v>5000</v>
+      </c>
+      <c r="E9">
+        <v>153</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>2.56</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>3.06</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B10">
+        <v>5000</v>
+      </c>
+      <c r="C10">
+        <v>111</v>
+      </c>
+      <c r="D10">
+        <v>5000</v>
+      </c>
+      <c r="E10">
+        <v>151</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>3.02</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B11">
+        <v>5000</v>
+      </c>
+      <c r="C11">
+        <v>112</v>
+      </c>
+      <c r="D11">
+        <v>5000</v>
+      </c>
+      <c r="E11">
+        <v>155</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>2.2399999999999998</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>3.1</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>45597</v>
+      </c>
+      <c r="B12">
+        <v>5000</v>
+      </c>
+      <c r="C12">
+        <v>117</v>
+      </c>
+      <c r="D12">
+        <v>5000</v>
+      </c>
+      <c r="E12">
+        <v>150</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B13">
+        <v>5000</v>
+      </c>
+      <c r="C13">
+        <v>110</v>
+      </c>
+      <c r="D13">
+        <v>5000</v>
+      </c>
+      <c r="E13">
+        <v>146</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>2.1999999999999997</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>2.92</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31740DA4-5403-4C55-A2BF-9FB7B71E2080}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -67692,7 +69296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939BF3C8-F88F-481C-9A2D-3E94D8007FA5}">
   <dimension ref="A1:S502"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -67758,7 +69362,7 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="e">
+      <c r="A2" t="e">
         <v>#REF!</v>
       </c>
       <c r="B2">
@@ -67798,12 +69402,12 @@
       <c r="R2" t="s">
         <v>2039</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2">
         <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" t="s">
         <v>1010</v>
       </c>
       <c r="B3">
@@ -67843,12 +69447,12 @@
       <c r="R3" t="s">
         <v>2040</v>
       </c>
-      <c r="S3" s="8">
+      <c r="S3">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" t="s">
         <v>1011</v>
       </c>
       <c r="B4">
@@ -67888,12 +69492,12 @@
       <c r="R4" t="s">
         <v>2041</v>
       </c>
-      <c r="S4" s="8">
+      <c r="S4">
         <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" t="s">
         <v>1012</v>
       </c>
       <c r="B5">
@@ -67932,7 +69536,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" t="s">
         <v>1013</v>
       </c>
       <c r="B6">
@@ -67971,7 +69575,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" t="s">
         <v>1014</v>
       </c>
       <c r="B7">
@@ -68010,7 +69614,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" t="s">
         <v>1015</v>
       </c>
       <c r="B8">
@@ -68049,7 +69653,7 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" t="s">
         <v>1016</v>
       </c>
       <c r="B9">
@@ -68088,7 +69692,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" t="s">
         <v>1017</v>
       </c>
       <c r="B10">
@@ -68127,7 +69731,7 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" t="s">
         <v>1018</v>
       </c>
       <c r="B11">
@@ -68166,7 +69770,7 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" t="s">
         <v>1019</v>
       </c>
       <c r="B12">
@@ -68205,7 +69809,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" t="s">
         <v>1020</v>
       </c>
       <c r="B13">
@@ -68244,7 +69848,7 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" t="s">
         <v>1021</v>
       </c>
       <c r="B14">
@@ -68283,7 +69887,7 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" t="s">
         <v>1022</v>
       </c>
       <c r="B15">
@@ -68322,7 +69926,7 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" t="s">
         <v>1023</v>
       </c>
       <c r="B16">
@@ -68361,7 +69965,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" t="s">
         <v>1024</v>
       </c>
       <c r="B17">
@@ -68400,7 +70004,7 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" t="s">
         <v>1025</v>
       </c>
       <c r="B18">
@@ -68439,7 +70043,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" t="s">
         <v>1026</v>
       </c>
       <c r="B19">
@@ -68478,7 +70082,7 @@
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" t="s">
         <v>1027</v>
       </c>
       <c r="B20">
@@ -68517,7 +70121,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" t="s">
         <v>1028</v>
       </c>
       <c r="B21">
@@ -68556,7 +70160,7 @@
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" t="s">
         <v>1029</v>
       </c>
       <c r="B22">
@@ -68595,7 +70199,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" t="s">
         <v>1030</v>
       </c>
       <c r="B23">
@@ -68634,7 +70238,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" t="s">
         <v>1031</v>
       </c>
       <c r="B24">
@@ -68673,7 +70277,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" t="s">
         <v>1032</v>
       </c>
       <c r="B25">
@@ -68712,7 +70316,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" t="s">
         <v>1033</v>
       </c>
       <c r="B26">
@@ -68751,7 +70355,7 @@
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" t="s">
         <v>1034</v>
       </c>
       <c r="B27">
@@ -68790,7 +70394,7 @@
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" t="s">
         <v>1035</v>
       </c>
       <c r="B28">
@@ -68829,7 +70433,7 @@
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" t="s">
         <v>1036</v>
       </c>
       <c r="B29">
@@ -68868,7 +70472,7 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" t="s">
         <v>1037</v>
       </c>
       <c r="B30">
@@ -68907,7 +70511,7 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" t="s">
         <v>1038</v>
       </c>
       <c r="B31">
@@ -68946,7 +70550,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" t="s">
         <v>1039</v>
       </c>
       <c r="B32">
@@ -68985,7 +70589,7 @@
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" t="s">
         <v>1040</v>
       </c>
       <c r="B33">
@@ -69024,7 +70628,7 @@
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" t="s">
         <v>1041</v>
       </c>
       <c r="B34">
@@ -69063,7 +70667,7 @@
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" t="s">
         <v>1042</v>
       </c>
       <c r="B35">
@@ -69102,7 +70706,7 @@
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" t="s">
         <v>1043</v>
       </c>
       <c r="B36">
@@ -69141,7 +70745,7 @@
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" t="s">
         <v>1044</v>
       </c>
       <c r="B37">
@@ -69180,7 +70784,7 @@
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" t="s">
         <v>1045</v>
       </c>
       <c r="B38">
@@ -69219,7 +70823,7 @@
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" t="s">
         <v>1046</v>
       </c>
       <c r="B39">
@@ -69258,7 +70862,7 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" t="s">
         <v>1047</v>
       </c>
       <c r="B40">
@@ -69297,7 +70901,7 @@
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" t="s">
         <v>1048</v>
       </c>
       <c r="B41">
@@ -69336,7 +70940,7 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+      <c r="A42" t="s">
         <v>1049</v>
       </c>
       <c r="B42">
@@ -69375,7 +70979,7 @@
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" t="s">
         <v>1050</v>
       </c>
       <c r="B43">
@@ -69414,7 +71018,7 @@
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" t="s">
         <v>1051</v>
       </c>
       <c r="B44">
@@ -69453,7 +71057,7 @@
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" t="s">
         <v>1052</v>
       </c>
       <c r="B45">
@@ -69492,7 +71096,7 @@
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="A46" t="s">
         <v>1053</v>
       </c>
       <c r="B46">
@@ -69531,7 +71135,7 @@
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" t="s">
         <v>1054</v>
       </c>
       <c r="B47">
@@ -69561,7 +71165,7 @@
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
+      <c r="A48" t="s">
         <v>1055</v>
       </c>
       <c r="B48">
@@ -69591,7 +71195,7 @@
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+      <c r="A49" t="s">
         <v>1056</v>
       </c>
       <c r="B49">
@@ -69621,7 +71225,7 @@
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
+      <c r="A50" t="s">
         <v>1057</v>
       </c>
       <c r="B50">
@@ -69651,7 +71255,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
+      <c r="A51" t="s">
         <v>1058</v>
       </c>
       <c r="B51">
@@ -69681,7 +71285,7 @@
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
+      <c r="A52" t="s">
         <v>1059</v>
       </c>
       <c r="B52">
@@ -69711,7 +71315,7 @@
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+      <c r="A53" t="s">
         <v>1060</v>
       </c>
       <c r="B53">
@@ -69741,7 +71345,7 @@
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="s">
+      <c r="A54" t="s">
         <v>1061</v>
       </c>
       <c r="B54">
@@ -69771,7 +71375,7 @@
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
+      <c r="A55" t="s">
         <v>1062</v>
       </c>
       <c r="B55">
@@ -69801,7 +71405,7 @@
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="8" t="s">
+      <c r="A56" t="s">
         <v>1063</v>
       </c>
       <c r="B56">
@@ -69831,7 +71435,7 @@
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
+      <c r="A57" t="s">
         <v>1064</v>
       </c>
       <c r="B57">
@@ -69861,7 +71465,7 @@
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
+      <c r="A58" t="s">
         <v>1065</v>
       </c>
       <c r="B58">
@@ -69891,7 +71495,7 @@
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="8" t="s">
+      <c r="A59" t="s">
         <v>1066</v>
       </c>
       <c r="B59">
@@ -69921,7 +71525,7 @@
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+      <c r="A60" t="s">
         <v>1067</v>
       </c>
       <c r="B60">
@@ -69951,7 +71555,7 @@
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="8" t="s">
+      <c r="A61" t="s">
         <v>1068</v>
       </c>
       <c r="B61">
@@ -69981,7 +71585,7 @@
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="8" t="s">
+      <c r="A62" t="s">
         <v>1069</v>
       </c>
       <c r="B62">
@@ -70011,7 +71615,7 @@
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="8" t="s">
+      <c r="A63" t="s">
         <v>1070</v>
       </c>
       <c r="B63">
@@ -70041,7 +71645,7 @@
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="8" t="s">
+      <c r="A64" t="s">
         <v>1071</v>
       </c>
       <c r="B64">
@@ -70071,7 +71675,7 @@
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="8" t="s">
+      <c r="A65" t="s">
         <v>1072</v>
       </c>
       <c r="B65">
@@ -70101,7 +71705,7 @@
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="8" t="s">
+      <c r="A66" t="s">
         <v>1073</v>
       </c>
       <c r="B66">
@@ -70131,7 +71735,7 @@
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" s="8" t="s">
+      <c r="A67" t="s">
         <v>1074</v>
       </c>
       <c r="B67">
@@ -70161,7 +71765,7 @@
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="8" t="s">
+      <c r="A68" t="s">
         <v>1075</v>
       </c>
       <c r="B68">
@@ -70191,7 +71795,7 @@
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="8" t="s">
+      <c r="A69" t="s">
         <v>1076</v>
       </c>
       <c r="B69">
@@ -70221,7 +71825,7 @@
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
+      <c r="A70" t="s">
         <v>1077</v>
       </c>
       <c r="B70">
@@ -70251,7 +71855,7 @@
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="s">
+      <c r="A71" t="s">
         <v>1078</v>
       </c>
       <c r="B71">
@@ -70281,7 +71885,7 @@
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
+      <c r="A72" t="s">
         <v>1079</v>
       </c>
       <c r="B72">
@@ -70311,7 +71915,7 @@
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A73" s="8" t="s">
+      <c r="A73" t="s">
         <v>1080</v>
       </c>
       <c r="B73">
@@ -70341,7 +71945,7 @@
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="s">
+      <c r="A74" t="s">
         <v>1081</v>
       </c>
       <c r="B74">
@@ -70371,7 +71975,7 @@
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75" s="8" t="s">
+      <c r="A75" t="s">
         <v>1082</v>
       </c>
       <c r="B75">
@@ -70401,7 +72005,7 @@
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
+      <c r="A76" t="s">
         <v>1083</v>
       </c>
       <c r="B76">
@@ -70431,7 +72035,7 @@
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="8" t="s">
+      <c r="A77" t="s">
         <v>1084</v>
       </c>
       <c r="B77">
@@ -70461,7 +72065,7 @@
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A78" s="8" t="s">
+      <c r="A78" t="s">
         <v>1085</v>
       </c>
       <c r="B78">
@@ -70491,7 +72095,7 @@
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="s">
+      <c r="A79" t="s">
         <v>1086</v>
       </c>
       <c r="B79">
@@ -70521,7 +72125,7 @@
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="s">
+      <c r="A80" t="s">
         <v>1087</v>
       </c>
       <c r="B80">
@@ -70551,7 +72155,7 @@
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A81" s="8" t="s">
+      <c r="A81" t="s">
         <v>1088</v>
       </c>
       <c r="B81">
@@ -70581,7 +72185,7 @@
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A82" s="8" t="s">
+      <c r="A82" t="s">
         <v>1089</v>
       </c>
       <c r="B82">
@@ -70611,7 +72215,7 @@
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A83" s="8" t="s">
+      <c r="A83" t="s">
         <v>1090</v>
       </c>
       <c r="B83">
@@ -70641,7 +72245,7 @@
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="s">
+      <c r="A84" t="s">
         <v>1091</v>
       </c>
       <c r="B84">
@@ -70671,7 +72275,7 @@
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="s">
+      <c r="A85" t="s">
         <v>1092</v>
       </c>
       <c r="B85">
@@ -70701,7 +72305,7 @@
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A86" s="8" t="s">
+      <c r="A86" t="s">
         <v>1093</v>
       </c>
       <c r="B86">
@@ -70731,7 +72335,7 @@
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A87" s="8" t="s">
+      <c r="A87" t="s">
         <v>1094</v>
       </c>
       <c r="B87">
@@ -70761,7 +72365,7 @@
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A88" s="8" t="s">
+      <c r="A88" t="s">
         <v>1095</v>
       </c>
       <c r="B88">
@@ -70791,7 +72395,7 @@
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A89" s="8" t="s">
+      <c r="A89" t="s">
         <v>1096</v>
       </c>
       <c r="B89">
@@ -70821,7 +72425,7 @@
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A90" s="8" t="s">
+      <c r="A90" t="s">
         <v>1097</v>
       </c>
       <c r="B90">
@@ -70851,7 +72455,7 @@
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A91" s="8" t="s">
+      <c r="A91" t="s">
         <v>1098</v>
       </c>
       <c r="B91">
@@ -70881,7 +72485,7 @@
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A92" s="8" t="s">
+      <c r="A92" t="s">
         <v>1099</v>
       </c>
       <c r="B92">
@@ -70911,7 +72515,7 @@
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A93" s="8" t="s">
+      <c r="A93" t="s">
         <v>1100</v>
       </c>
       <c r="B93">
@@ -70941,7 +72545,7 @@
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94" s="8" t="s">
+      <c r="A94" t="s">
         <v>1101</v>
       </c>
       <c r="B94">
@@ -70971,7 +72575,7 @@
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="s">
+      <c r="A95" t="s">
         <v>1102</v>
       </c>
       <c r="B95">
@@ -71001,7 +72605,7 @@
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A96" s="8" t="s">
+      <c r="A96" t="s">
         <v>1103</v>
       </c>
       <c r="B96">
@@ -71031,7 +72635,7 @@
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A97" s="8" t="s">
+      <c r="A97" t="s">
         <v>1104</v>
       </c>
       <c r="B97">
@@ -71061,7 +72665,7 @@
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="s">
+      <c r="A98" t="s">
         <v>1105</v>
       </c>
       <c r="B98">
@@ -71091,7 +72695,7 @@
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A99" s="8" t="s">
+      <c r="A99" t="s">
         <v>1106</v>
       </c>
       <c r="B99">
@@ -71121,7 +72725,7 @@
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A100" s="8" t="s">
+      <c r="A100" t="s">
         <v>1107</v>
       </c>
       <c r="B100">
@@ -71151,7 +72755,7 @@
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="s">
+      <c r="A101" t="s">
         <v>1108</v>
       </c>
       <c r="B101">
@@ -71181,7 +72785,7 @@
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A102" s="8" t="s">
+      <c r="A102" t="s">
         <v>1109</v>
       </c>
       <c r="B102">
@@ -71211,7 +72815,7 @@
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103" s="8" t="s">
+      <c r="A103" t="s">
         <v>1110</v>
       </c>
       <c r="B103">
@@ -71241,7 +72845,7 @@
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
+      <c r="A104" t="s">
         <v>1111</v>
       </c>
       <c r="B104">
@@ -71271,7 +72875,7 @@
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A105" s="8" t="s">
+      <c r="A105" t="s">
         <v>1112</v>
       </c>
       <c r="B105">
@@ -71301,7 +72905,7 @@
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106" s="8" t="s">
+      <c r="A106" t="s">
         <v>1113</v>
       </c>
       <c r="B106">
@@ -71331,7 +72935,7 @@
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107" s="8" t="s">
+      <c r="A107" t="s">
         <v>1114</v>
       </c>
       <c r="B107">
@@ -71361,7 +72965,7 @@
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108" s="8" t="s">
+      <c r="A108" t="s">
         <v>1115</v>
       </c>
       <c r="B108">
@@ -71391,7 +72995,7 @@
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A109" s="8" t="s">
+      <c r="A109" t="s">
         <v>1116</v>
       </c>
       <c r="B109">
@@ -71421,7 +73025,7 @@
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A110" s="8" t="s">
+      <c r="A110" t="s">
         <v>1117</v>
       </c>
       <c r="B110">
@@ -71451,7 +73055,7 @@
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A111" s="8" t="s">
+      <c r="A111" t="s">
         <v>1118</v>
       </c>
       <c r="B111">
@@ -71481,7 +73085,7 @@
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A112" s="8" t="s">
+      <c r="A112" t="s">
         <v>1119</v>
       </c>
       <c r="B112">
@@ -71511,7 +73115,7 @@
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A113" s="8" t="s">
+      <c r="A113" t="s">
         <v>1120</v>
       </c>
       <c r="B113">
@@ -71541,7 +73145,7 @@
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A114" s="8" t="s">
+      <c r="A114" t="s">
         <v>1121</v>
       </c>
       <c r="B114">
@@ -71571,7 +73175,7 @@
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A115" s="8" t="s">
+      <c r="A115" t="s">
         <v>1122</v>
       </c>
       <c r="B115">
@@ -71601,7 +73205,7 @@
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A116" s="8" t="s">
+      <c r="A116" t="s">
         <v>1123</v>
       </c>
       <c r="B116">
@@ -71631,7 +73235,7 @@
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A117" s="8" t="s">
+      <c r="A117" t="s">
         <v>1124</v>
       </c>
       <c r="B117">
@@ -71661,7 +73265,7 @@
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A118" s="8" t="s">
+      <c r="A118" t="s">
         <v>1125</v>
       </c>
       <c r="B118">
@@ -71691,7 +73295,7 @@
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A119" s="8" t="s">
+      <c r="A119" t="s">
         <v>1126</v>
       </c>
       <c r="B119">
@@ -71721,7 +73325,7 @@
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A120" s="8" t="s">
+      <c r="A120" t="s">
         <v>1127</v>
       </c>
       <c r="B120">
@@ -71751,7 +73355,7 @@
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A121" s="8" t="s">
+      <c r="A121" t="s">
         <v>1128</v>
       </c>
       <c r="B121">
@@ -71781,7 +73385,7 @@
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A122" s="8" t="s">
+      <c r="A122" t="s">
         <v>1129</v>
       </c>
       <c r="B122">
@@ -71811,7 +73415,7 @@
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A123" s="8" t="s">
+      <c r="A123" t="s">
         <v>1130</v>
       </c>
       <c r="B123">
@@ -71841,7 +73445,7 @@
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A124" s="8" t="s">
+      <c r="A124" t="s">
         <v>1131</v>
       </c>
       <c r="B124">
@@ -71871,7 +73475,7 @@
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A125" s="8" t="s">
+      <c r="A125" t="s">
         <v>1132</v>
       </c>
       <c r="B125">
@@ -71901,7 +73505,7 @@
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A126" s="8" t="s">
+      <c r="A126" t="s">
         <v>1133</v>
       </c>
       <c r="B126">
@@ -71931,7 +73535,7 @@
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A127" s="8" t="s">
+      <c r="A127" t="s">
         <v>1134</v>
       </c>
       <c r="B127">
@@ -71961,7 +73565,7 @@
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A128" s="8" t="s">
+      <c r="A128" t="s">
         <v>1135</v>
       </c>
       <c r="B128">
@@ -71991,7 +73595,7 @@
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A129" s="8" t="s">
+      <c r="A129" t="s">
         <v>1136</v>
       </c>
       <c r="B129">
@@ -72021,7 +73625,7 @@
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A130" s="8" t="s">
+      <c r="A130" t="s">
         <v>1137</v>
       </c>
       <c r="B130">
@@ -72051,7 +73655,7 @@
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A131" s="8" t="s">
+      <c r="A131" t="s">
         <v>1138</v>
       </c>
       <c r="B131">
@@ -72081,7 +73685,7 @@
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A132" s="8" t="s">
+      <c r="A132" t="s">
         <v>1139</v>
       </c>
       <c r="B132">
@@ -72111,7 +73715,7 @@
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A133" s="8" t="s">
+      <c r="A133" t="s">
         <v>1140</v>
       </c>
       <c r="B133">
@@ -72141,7 +73745,7 @@
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A134" s="8" t="s">
+      <c r="A134" t="s">
         <v>1141</v>
       </c>
       <c r="B134">
@@ -72171,7 +73775,7 @@
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A135" s="8" t="s">
+      <c r="A135" t="s">
         <v>1142</v>
       </c>
       <c r="B135">
@@ -72201,7 +73805,7 @@
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A136" s="8" t="s">
+      <c r="A136" t="s">
         <v>1143</v>
       </c>
       <c r="B136">
@@ -72231,7 +73835,7 @@
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A137" s="8" t="s">
+      <c r="A137" t="s">
         <v>1144</v>
       </c>
       <c r="B137">
@@ -72261,7 +73865,7 @@
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A138" s="8" t="s">
+      <c r="A138" t="s">
         <v>1145</v>
       </c>
       <c r="B138">
@@ -72291,7 +73895,7 @@
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A139" s="8" t="s">
+      <c r="A139" t="s">
         <v>1146</v>
       </c>
       <c r="B139">
@@ -72321,7 +73925,7 @@
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A140" s="8" t="s">
+      <c r="A140" t="s">
         <v>1147</v>
       </c>
       <c r="B140">
@@ -72351,7 +73955,7 @@
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A141" s="8" t="s">
+      <c r="A141" t="s">
         <v>1148</v>
       </c>
       <c r="B141">
@@ -72381,7 +73985,7 @@
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A142" s="8" t="s">
+      <c r="A142" t="s">
         <v>1149</v>
       </c>
       <c r="B142">
@@ -72411,7 +74015,7 @@
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A143" s="8" t="s">
+      <c r="A143" t="s">
         <v>1150</v>
       </c>
       <c r="B143">
@@ -72441,7 +74045,7 @@
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A144" s="8" t="s">
+      <c r="A144" t="s">
         <v>1151</v>
       </c>
       <c r="B144">
@@ -72471,7 +74075,7 @@
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A145" s="8" t="s">
+      <c r="A145" t="s">
         <v>1152</v>
       </c>
       <c r="B145">
@@ -72501,7 +74105,7 @@
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A146" s="8" t="s">
+      <c r="A146" t="s">
         <v>1153</v>
       </c>
       <c r="B146">
@@ -72531,7 +74135,7 @@
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A147" s="8" t="s">
+      <c r="A147" t="s">
         <v>1154</v>
       </c>
       <c r="B147">
@@ -72561,7 +74165,7 @@
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A148" s="8" t="s">
+      <c r="A148" t="s">
         <v>1155</v>
       </c>
       <c r="B148">
@@ -72591,7 +74195,7 @@
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A149" s="8" t="s">
+      <c r="A149" t="s">
         <v>1156</v>
       </c>
       <c r="B149">
@@ -72621,7 +74225,7 @@
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A150" s="8" t="s">
+      <c r="A150" t="s">
         <v>1157</v>
       </c>
       <c r="B150">
@@ -72651,7 +74255,7 @@
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A151" s="8" t="s">
+      <c r="A151" t="s">
         <v>1158</v>
       </c>
       <c r="B151">
@@ -72681,7 +74285,7 @@
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A152" s="8" t="s">
+      <c r="A152" t="s">
         <v>1159</v>
       </c>
       <c r="B152">
@@ -72711,7 +74315,7 @@
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A153" s="8" t="s">
+      <c r="A153" t="s">
         <v>1160</v>
       </c>
       <c r="B153">
@@ -72741,7 +74345,7 @@
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A154" s="8" t="s">
+      <c r="A154" t="s">
         <v>1161</v>
       </c>
       <c r="B154">
@@ -72771,7 +74375,7 @@
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A155" s="8" t="s">
+      <c r="A155" t="s">
         <v>1162</v>
       </c>
       <c r="B155">
@@ -72801,7 +74405,7 @@
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A156" s="8" t="s">
+      <c r="A156" t="s">
         <v>1163</v>
       </c>
       <c r="B156">
@@ -72831,7 +74435,7 @@
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A157" s="8" t="s">
+      <c r="A157" t="s">
         <v>1164</v>
       </c>
       <c r="B157">
@@ -72861,7 +74465,7 @@
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A158" s="8" t="s">
+      <c r="A158" t="s">
         <v>1165</v>
       </c>
       <c r="B158">
@@ -72891,7 +74495,7 @@
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A159" s="8" t="s">
+      <c r="A159" t="s">
         <v>1166</v>
       </c>
       <c r="B159">
@@ -72921,7 +74525,7 @@
       </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A160" s="8" t="s">
+      <c r="A160" t="s">
         <v>1167</v>
       </c>
       <c r="B160">
@@ -72951,7 +74555,7 @@
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A161" s="8" t="s">
+      <c r="A161" t="s">
         <v>1168</v>
       </c>
       <c r="B161">
@@ -72981,7 +74585,7 @@
       </c>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A162" s="8" t="s">
+      <c r="A162" t="s">
         <v>1169</v>
       </c>
       <c r="B162">
@@ -73011,7 +74615,7 @@
       </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A163" s="8" t="s">
+      <c r="A163" t="s">
         <v>1170</v>
       </c>
       <c r="B163">
@@ -73041,7 +74645,7 @@
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A164" s="8" t="s">
+      <c r="A164" t="s">
         <v>1171</v>
       </c>
       <c r="B164">
@@ -73071,7 +74675,7 @@
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A165" s="8" t="s">
+      <c r="A165" t="s">
         <v>1172</v>
       </c>
       <c r="B165">
@@ -73101,7 +74705,7 @@
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A166" s="8" t="s">
+      <c r="A166" t="s">
         <v>1173</v>
       </c>
       <c r="B166">
@@ -73131,7 +74735,7 @@
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A167" s="8" t="s">
+      <c r="A167" t="s">
         <v>1174</v>
       </c>
       <c r="B167">
@@ -73161,7 +74765,7 @@
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A168" s="8" t="s">
+      <c r="A168" t="s">
         <v>1175</v>
       </c>
       <c r="B168">
@@ -73191,7 +74795,7 @@
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A169" s="8" t="s">
+      <c r="A169" t="s">
         <v>1176</v>
       </c>
       <c r="B169">
@@ -73221,7 +74825,7 @@
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A170" s="8" t="s">
+      <c r="A170" t="s">
         <v>1177</v>
       </c>
       <c r="B170">
@@ -73251,7 +74855,7 @@
       </c>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A171" s="8" t="s">
+      <c r="A171" t="s">
         <v>1178</v>
       </c>
       <c r="B171">
@@ -73281,7 +74885,7 @@
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A172" s="8" t="s">
+      <c r="A172" t="s">
         <v>1179</v>
       </c>
       <c r="B172">
@@ -73311,7 +74915,7 @@
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A173" s="8" t="s">
+      <c r="A173" t="s">
         <v>1180</v>
       </c>
       <c r="B173">
@@ -73341,7 +74945,7 @@
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A174" s="8" t="s">
+      <c r="A174" t="s">
         <v>1181</v>
       </c>
       <c r="B174">
@@ -73371,7 +74975,7 @@
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A175" s="8" t="s">
+      <c r="A175" t="s">
         <v>1182</v>
       </c>
       <c r="B175">
@@ -73401,7 +75005,7 @@
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A176" s="8" t="s">
+      <c r="A176" t="s">
         <v>1183</v>
       </c>
       <c r="B176">
@@ -73431,7 +75035,7 @@
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A177" s="8" t="s">
+      <c r="A177" t="s">
         <v>1184</v>
       </c>
       <c r="B177">
@@ -73461,7 +75065,7 @@
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A178" s="8" t="s">
+      <c r="A178" t="s">
         <v>1185</v>
       </c>
       <c r="B178">
@@ -73491,7 +75095,7 @@
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A179" s="8" t="s">
+      <c r="A179" t="s">
         <v>1186</v>
       </c>
       <c r="B179">
@@ -73521,7 +75125,7 @@
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A180" s="8" t="s">
+      <c r="A180" t="s">
         <v>1187</v>
       </c>
       <c r="B180">
@@ -73551,7 +75155,7 @@
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A181" s="8" t="s">
+      <c r="A181" t="s">
         <v>1188</v>
       </c>
       <c r="B181">
@@ -73581,7 +75185,7 @@
       </c>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A182" s="8" t="s">
+      <c r="A182" t="s">
         <v>1189</v>
       </c>
       <c r="B182">
@@ -73611,7 +75215,7 @@
       </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A183" s="8" t="s">
+      <c r="A183" t="s">
         <v>1190</v>
       </c>
       <c r="B183">
@@ -73641,7 +75245,7 @@
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A184" s="8" t="s">
+      <c r="A184" t="s">
         <v>1191</v>
       </c>
       <c r="B184">
@@ -73671,7 +75275,7 @@
       </c>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A185" s="8" t="s">
+      <c r="A185" t="s">
         <v>1192</v>
       </c>
       <c r="B185">
@@ -73701,7 +75305,7 @@
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A186" s="8" t="s">
+      <c r="A186" t="s">
         <v>1193</v>
       </c>
       <c r="B186">
@@ -73731,7 +75335,7 @@
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A187" s="8" t="s">
+      <c r="A187" t="s">
         <v>1194</v>
       </c>
       <c r="B187">
@@ -73761,7 +75365,7 @@
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A188" s="8" t="s">
+      <c r="A188" t="s">
         <v>1195</v>
       </c>
       <c r="B188">
@@ -73791,7 +75395,7 @@
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A189" s="8" t="s">
+      <c r="A189" t="s">
         <v>1196</v>
       </c>
       <c r="B189">
@@ -73821,7 +75425,7 @@
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A190" s="8" t="s">
+      <c r="A190" t="s">
         <v>1197</v>
       </c>
       <c r="B190">
@@ -73851,7 +75455,7 @@
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A191" s="8" t="s">
+      <c r="A191" t="s">
         <v>1198</v>
       </c>
       <c r="B191">
@@ -73881,7 +75485,7 @@
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A192" s="8" t="s">
+      <c r="A192" t="s">
         <v>1199</v>
       </c>
       <c r="B192">
@@ -73911,7 +75515,7 @@
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A193" s="8" t="s">
+      <c r="A193" t="s">
         <v>1200</v>
       </c>
       <c r="B193">
@@ -73941,7 +75545,7 @@
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A194" s="8" t="s">
+      <c r="A194" t="s">
         <v>1201</v>
       </c>
       <c r="B194">
@@ -73971,7 +75575,7 @@
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A195" s="8" t="s">
+      <c r="A195" t="s">
         <v>1202</v>
       </c>
       <c r="B195">
@@ -74001,7 +75605,7 @@
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A196" s="8" t="s">
+      <c r="A196" t="s">
         <v>1203</v>
       </c>
       <c r="B196">
@@ -74031,7 +75635,7 @@
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A197" s="8" t="s">
+      <c r="A197" t="s">
         <v>1204</v>
       </c>
       <c r="B197">
@@ -74061,7 +75665,7 @@
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A198" s="8" t="s">
+      <c r="A198" t="s">
         <v>1205</v>
       </c>
       <c r="B198">
@@ -74091,7 +75695,7 @@
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A199" s="8" t="s">
+      <c r="A199" t="s">
         <v>1206</v>
       </c>
       <c r="B199">
@@ -74121,7 +75725,7 @@
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A200" s="8" t="s">
+      <c r="A200" t="s">
         <v>1207</v>
       </c>
       <c r="B200">
@@ -74151,7 +75755,7 @@
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A201" s="8" t="s">
+      <c r="A201" t="s">
         <v>1208</v>
       </c>
       <c r="B201">
@@ -74181,7 +75785,7 @@
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A202" s="8" t="s">
+      <c r="A202" t="s">
         <v>1209</v>
       </c>
       <c r="B202">
@@ -74211,7 +75815,7 @@
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A203" s="8" t="s">
+      <c r="A203" t="s">
         <v>1210</v>
       </c>
       <c r="B203">
@@ -74241,7 +75845,7 @@
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A204" s="8" t="s">
+      <c r="A204" t="s">
         <v>1211</v>
       </c>
       <c r="B204">
@@ -74271,7 +75875,7 @@
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A205" s="8" t="s">
+      <c r="A205" t="s">
         <v>1212</v>
       </c>
       <c r="B205">
@@ -74301,7 +75905,7 @@
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A206" s="8" t="s">
+      <c r="A206" t="s">
         <v>1213</v>
       </c>
       <c r="B206">
@@ -74331,7 +75935,7 @@
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A207" s="8" t="s">
+      <c r="A207" t="s">
         <v>1214</v>
       </c>
       <c r="B207">
@@ -74361,7 +75965,7 @@
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A208" s="8" t="s">
+      <c r="A208" t="s">
         <v>1215</v>
       </c>
       <c r="B208">
@@ -74391,7 +75995,7 @@
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A209" s="8" t="s">
+      <c r="A209" t="s">
         <v>1216</v>
       </c>
       <c r="B209">
@@ -74421,7 +76025,7 @@
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A210" s="8" t="s">
+      <c r="A210" t="s">
         <v>1217</v>
       </c>
       <c r="B210">
@@ -74451,7 +76055,7 @@
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A211" s="8" t="s">
+      <c r="A211" t="s">
         <v>1218</v>
       </c>
       <c r="B211">
@@ -74481,7 +76085,7 @@
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A212" s="8" t="s">
+      <c r="A212" t="s">
         <v>1219</v>
       </c>
       <c r="B212">
@@ -74511,7 +76115,7 @@
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A213" s="8" t="s">
+      <c r="A213" t="s">
         <v>1220</v>
       </c>
       <c r="B213">
@@ -74541,7 +76145,7 @@
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A214" s="8" t="s">
+      <c r="A214" t="s">
         <v>1221</v>
       </c>
       <c r="B214">
@@ -74571,7 +76175,7 @@
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A215" s="8" t="s">
+      <c r="A215" t="s">
         <v>1222</v>
       </c>
       <c r="B215">
@@ -74601,7 +76205,7 @@
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A216" s="8" t="s">
+      <c r="A216" t="s">
         <v>1223</v>
       </c>
       <c r="B216">
@@ -74631,7 +76235,7 @@
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A217" s="8" t="s">
+      <c r="A217" t="s">
         <v>1224</v>
       </c>
       <c r="B217">
@@ -74661,7 +76265,7 @@
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A218" s="8" t="s">
+      <c r="A218" t="s">
         <v>1225</v>
       </c>
       <c r="B218">
@@ -74691,7 +76295,7 @@
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A219" s="8" t="s">
+      <c r="A219" t="s">
         <v>1226</v>
       </c>
       <c r="B219">
@@ -74721,7 +76325,7 @@
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A220" s="8" t="s">
+      <c r="A220" t="s">
         <v>1227</v>
       </c>
       <c r="B220">
@@ -74751,7 +76355,7 @@
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A221" s="8" t="s">
+      <c r="A221" t="s">
         <v>1228</v>
       </c>
       <c r="B221">
@@ -74781,7 +76385,7 @@
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A222" s="8" t="s">
+      <c r="A222" t="s">
         <v>1229</v>
       </c>
       <c r="B222">
@@ -74811,7 +76415,7 @@
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A223" s="8" t="s">
+      <c r="A223" t="s">
         <v>1230</v>
       </c>
       <c r="B223">
@@ -74841,7 +76445,7 @@
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A224" s="8" t="s">
+      <c r="A224" t="s">
         <v>1231</v>
       </c>
       <c r="B224">
@@ -74871,7 +76475,7 @@
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A225" s="8" t="s">
+      <c r="A225" t="s">
         <v>1232</v>
       </c>
       <c r="B225">
@@ -74901,7 +76505,7 @@
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A226" s="8" t="s">
+      <c r="A226" t="s">
         <v>1233</v>
       </c>
       <c r="B226">
@@ -74931,7 +76535,7 @@
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A227" s="8" t="s">
+      <c r="A227" t="s">
         <v>1234</v>
       </c>
       <c r="B227">
@@ -74961,7 +76565,7 @@
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A228" s="8" t="s">
+      <c r="A228" t="s">
         <v>1235</v>
       </c>
       <c r="B228">
@@ -74991,7 +76595,7 @@
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A229" s="8" t="s">
+      <c r="A229" t="s">
         <v>1236</v>
       </c>
       <c r="B229">
@@ -75021,7 +76625,7 @@
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A230" s="8" t="s">
+      <c r="A230" t="s">
         <v>1237</v>
       </c>
       <c r="B230">
@@ -75051,7 +76655,7 @@
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A231" s="8" t="s">
+      <c r="A231" t="s">
         <v>1238</v>
       </c>
       <c r="B231">
@@ -75081,7 +76685,7 @@
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A232" s="8" t="s">
+      <c r="A232" t="s">
         <v>1239</v>
       </c>
       <c r="B232">
@@ -75111,7 +76715,7 @@
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A233" s="8" t="s">
+      <c r="A233" t="s">
         <v>1240</v>
       </c>
       <c r="B233">
@@ -75141,7 +76745,7 @@
       </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A234" s="8" t="s">
+      <c r="A234" t="s">
         <v>1241</v>
       </c>
       <c r="B234">
@@ -75171,7 +76775,7 @@
       </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A235" s="8" t="s">
+      <c r="A235" t="s">
         <v>1242</v>
       </c>
       <c r="B235">
@@ -75201,7 +76805,7 @@
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A236" s="8" t="s">
+      <c r="A236" t="s">
         <v>1243</v>
       </c>
       <c r="B236">
@@ -75231,7 +76835,7 @@
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A237" s="8" t="s">
+      <c r="A237" t="s">
         <v>1244</v>
       </c>
       <c r="B237">
@@ -75261,7 +76865,7 @@
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A238" s="8" t="s">
+      <c r="A238" t="s">
         <v>1245</v>
       </c>
       <c r="B238">
@@ -75291,7 +76895,7 @@
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A239" s="8" t="s">
+      <c r="A239" t="s">
         <v>1246</v>
       </c>
       <c r="B239">
@@ -75321,7 +76925,7 @@
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A240" s="8" t="s">
+      <c r="A240" t="s">
         <v>1247</v>
       </c>
       <c r="B240">
@@ -75351,7 +76955,7 @@
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A241" s="8" t="s">
+      <c r="A241" t="s">
         <v>1248</v>
       </c>
       <c r="B241">
@@ -75381,7 +76985,7 @@
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A242" s="8" t="s">
+      <c r="A242" t="s">
         <v>1249</v>
       </c>
       <c r="B242">
@@ -75411,7 +77015,7 @@
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A243" s="8" t="s">
+      <c r="A243" t="s">
         <v>1250</v>
       </c>
       <c r="B243">
@@ -75441,7 +77045,7 @@
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A244" s="8" t="s">
+      <c r="A244" t="s">
         <v>1251</v>
       </c>
       <c r="B244">
@@ -75471,7 +77075,7 @@
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A245" s="8" t="s">
+      <c r="A245" t="s">
         <v>1252</v>
       </c>
       <c r="B245">
@@ -75501,7 +77105,7 @@
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A246" s="8" t="s">
+      <c r="A246" t="s">
         <v>1253</v>
       </c>
       <c r="B246">
@@ -75531,7 +77135,7 @@
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A247" s="8" t="s">
+      <c r="A247" t="s">
         <v>1254</v>
       </c>
       <c r="B247">
@@ -75561,7 +77165,7 @@
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A248" s="8" t="s">
+      <c r="A248" t="s">
         <v>1255</v>
       </c>
       <c r="B248">
@@ -75591,7 +77195,7 @@
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A249" s="8" t="s">
+      <c r="A249" t="s">
         <v>1256</v>
       </c>
       <c r="B249">
@@ -75621,7 +77225,7 @@
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A250" s="8" t="s">
+      <c r="A250" t="s">
         <v>1257</v>
       </c>
       <c r="B250">
@@ -75651,7 +77255,7 @@
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A251" s="8" t="s">
+      <c r="A251" t="s">
         <v>1258</v>
       </c>
       <c r="B251">
@@ -75681,7 +77285,7 @@
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A252" s="8" t="s">
+      <c r="A252" t="s">
         <v>1259</v>
       </c>
       <c r="B252">
@@ -75711,7 +77315,7 @@
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A253" s="8" t="s">
+      <c r="A253" t="s">
         <v>1260</v>
       </c>
       <c r="B253">
@@ -75741,7 +77345,7 @@
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A254" s="8" t="s">
+      <c r="A254" t="s">
         <v>1261</v>
       </c>
       <c r="B254">
@@ -75771,7 +77375,7 @@
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A255" s="8" t="s">
+      <c r="A255" t="s">
         <v>1262</v>
       </c>
       <c r="B255">
@@ -75801,7 +77405,7 @@
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A256" s="8" t="s">
+      <c r="A256" t="s">
         <v>1263</v>
       </c>
       <c r="B256">
@@ -75831,7 +77435,7 @@
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A257" s="8" t="s">
+      <c r="A257" t="s">
         <v>1264</v>
       </c>
       <c r="B257">
@@ -75861,7 +77465,7 @@
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A258" s="8" t="s">
+      <c r="A258" t="s">
         <v>1265</v>
       </c>
       <c r="B258">
@@ -75891,7 +77495,7 @@
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A259" s="8" t="s">
+      <c r="A259" t="s">
         <v>1266</v>
       </c>
       <c r="B259">
@@ -75921,7 +77525,7 @@
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A260" s="8" t="s">
+      <c r="A260" t="s">
         <v>1267</v>
       </c>
       <c r="B260">
@@ -75951,7 +77555,7 @@
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A261" s="8" t="s">
+      <c r="A261" t="s">
         <v>1268</v>
       </c>
       <c r="B261">
@@ -75981,7 +77585,7 @@
       </c>
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A262" s="8" t="s">
+      <c r="A262" t="s">
         <v>1269</v>
       </c>
       <c r="B262">
@@ -76011,7 +77615,7 @@
       </c>
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A263" s="8" t="s">
+      <c r="A263" t="s">
         <v>1270</v>
       </c>
       <c r="B263">
@@ -76041,7 +77645,7 @@
       </c>
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A264" s="8" t="s">
+      <c r="A264" t="s">
         <v>1271</v>
       </c>
       <c r="B264">
@@ -76071,7 +77675,7 @@
       </c>
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A265" s="8" t="s">
+      <c r="A265" t="s">
         <v>1272</v>
       </c>
       <c r="B265">
@@ -76101,7 +77705,7 @@
       </c>
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A266" s="8" t="s">
+      <c r="A266" t="s">
         <v>1273</v>
       </c>
       <c r="B266">
@@ -76131,7 +77735,7 @@
       </c>
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A267" s="8" t="s">
+      <c r="A267" t="s">
         <v>1274</v>
       </c>
       <c r="B267">
@@ -76161,7 +77765,7 @@
       </c>
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A268" s="8" t="s">
+      <c r="A268" t="s">
         <v>1275</v>
       </c>
       <c r="B268">
@@ -76191,7 +77795,7 @@
       </c>
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A269" s="8" t="s">
+      <c r="A269" t="s">
         <v>1276</v>
       </c>
       <c r="B269">
@@ -76221,7 +77825,7 @@
       </c>
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A270" s="8" t="s">
+      <c r="A270" t="s">
         <v>1277</v>
       </c>
       <c r="B270">
@@ -76251,7 +77855,7 @@
       </c>
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A271" s="8" t="s">
+      <c r="A271" t="s">
         <v>1278</v>
       </c>
       <c r="B271">
@@ -76281,7 +77885,7 @@
       </c>
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A272" s="8" t="s">
+      <c r="A272" t="s">
         <v>1279</v>
       </c>
       <c r="B272">
@@ -76311,7 +77915,7 @@
       </c>
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A273" s="8" t="s">
+      <c r="A273" t="s">
         <v>1280</v>
       </c>
       <c r="B273">
@@ -76341,7 +77945,7 @@
       </c>
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A274" s="8" t="s">
+      <c r="A274" t="s">
         <v>1281</v>
       </c>
       <c r="B274">
@@ -76371,7 +77975,7 @@
       </c>
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A275" s="8" t="s">
+      <c r="A275" t="s">
         <v>1282</v>
       </c>
       <c r="B275">
@@ -76401,7 +78005,7 @@
       </c>
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A276" s="8" t="s">
+      <c r="A276" t="s">
         <v>1283</v>
       </c>
       <c r="B276">
@@ -76431,7 +78035,7 @@
       </c>
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A277" s="8" t="s">
+      <c r="A277" t="s">
         <v>1284</v>
       </c>
       <c r="B277">
@@ -76461,7 +78065,7 @@
       </c>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A278" s="8" t="s">
+      <c r="A278" t="s">
         <v>1285</v>
       </c>
       <c r="B278">
@@ -76491,7 +78095,7 @@
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A279" s="8" t="s">
+      <c r="A279" t="s">
         <v>1286</v>
       </c>
       <c r="B279">
@@ -76521,7 +78125,7 @@
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A280" s="8" t="s">
+      <c r="A280" t="s">
         <v>1287</v>
       </c>
       <c r="B280">
@@ -76551,7 +78155,7 @@
       </c>
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A281" s="8" t="s">
+      <c r="A281" t="s">
         <v>1288</v>
       </c>
       <c r="B281">
@@ -76581,7 +78185,7 @@
       </c>
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A282" s="8" t="s">
+      <c r="A282" t="s">
         <v>1289</v>
       </c>
       <c r="B282">
@@ -76611,7 +78215,7 @@
       </c>
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A283" s="8" t="s">
+      <c r="A283" t="s">
         <v>1290</v>
       </c>
       <c r="B283">
@@ -76641,7 +78245,7 @@
       </c>
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A284" s="8" t="s">
+      <c r="A284" t="s">
         <v>1291</v>
       </c>
       <c r="B284">
@@ -76671,7 +78275,7 @@
       </c>
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A285" s="8" t="s">
+      <c r="A285" t="s">
         <v>1292</v>
       </c>
       <c r="B285">
@@ -76701,7 +78305,7 @@
       </c>
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A286" s="8" t="s">
+      <c r="A286" t="s">
         <v>1293</v>
       </c>
       <c r="B286">
@@ -76731,7 +78335,7 @@
       </c>
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A287" s="8" t="s">
+      <c r="A287" t="s">
         <v>1294</v>
       </c>
       <c r="B287">
@@ -76761,7 +78365,7 @@
       </c>
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A288" s="8" t="s">
+      <c r="A288" t="s">
         <v>1295</v>
       </c>
       <c r="B288">
@@ -76791,7 +78395,7 @@
       </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A289" s="8" t="s">
+      <c r="A289" t="s">
         <v>1296</v>
       </c>
       <c r="B289">
@@ -76821,7 +78425,7 @@
       </c>
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A290" s="8" t="s">
+      <c r="A290" t="s">
         <v>1297</v>
       </c>
       <c r="B290">
@@ -76851,7 +78455,7 @@
       </c>
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A291" s="8" t="s">
+      <c r="A291" t="s">
         <v>1298</v>
       </c>
       <c r="B291">
@@ -76881,7 +78485,7 @@
       </c>
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A292" s="8" t="s">
+      <c r="A292" t="s">
         <v>1299</v>
       </c>
       <c r="B292">
@@ -76911,7 +78515,7 @@
       </c>
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A293" s="8" t="s">
+      <c r="A293" t="s">
         <v>1300</v>
       </c>
       <c r="B293">
@@ -76941,7 +78545,7 @@
       </c>
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A294" s="8" t="s">
+      <c r="A294" t="s">
         <v>1301</v>
       </c>
       <c r="B294">
@@ -76971,7 +78575,7 @@
       </c>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A295" s="8" t="s">
+      <c r="A295" t="s">
         <v>1302</v>
       </c>
       <c r="B295">
@@ -77001,7 +78605,7 @@
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A296" s="8" t="s">
+      <c r="A296" t="s">
         <v>1303</v>
       </c>
       <c r="B296">
@@ -77031,7 +78635,7 @@
       </c>
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A297" s="8" t="s">
+      <c r="A297" t="s">
         <v>1304</v>
       </c>
       <c r="B297">
@@ -77061,7 +78665,7 @@
       </c>
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A298" s="8" t="s">
+      <c r="A298" t="s">
         <v>1305</v>
       </c>
       <c r="B298">
@@ -77091,7 +78695,7 @@
       </c>
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A299" s="8" t="s">
+      <c r="A299" t="s">
         <v>1306</v>
       </c>
       <c r="B299">
@@ -77121,7 +78725,7 @@
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A300" s="8" t="s">
+      <c r="A300" t="s">
         <v>1307</v>
       </c>
       <c r="B300">
@@ -77151,7 +78755,7 @@
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A301" s="8" t="s">
+      <c r="A301" t="s">
         <v>1308</v>
       </c>
       <c r="B301">
@@ -77181,7 +78785,7 @@
       </c>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A302" s="8" t="s">
+      <c r="A302" t="s">
         <v>1309</v>
       </c>
       <c r="B302">
@@ -77211,7 +78815,7 @@
       </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A303" s="8" t="s">
+      <c r="A303" t="s">
         <v>1310</v>
       </c>
       <c r="B303">
@@ -77241,7 +78845,7 @@
       </c>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A304" s="8" t="s">
+      <c r="A304" t="s">
         <v>1311</v>
       </c>
       <c r="B304">
@@ -77271,7 +78875,7 @@
       </c>
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A305" s="8" t="s">
+      <c r="A305" t="s">
         <v>1312</v>
       </c>
       <c r="B305">
@@ -77301,7 +78905,7 @@
       </c>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A306" s="8" t="s">
+      <c r="A306" t="s">
         <v>1313</v>
       </c>
       <c r="B306">
@@ -77331,7 +78935,7 @@
       </c>
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A307" s="8" t="s">
+      <c r="A307" t="s">
         <v>1314</v>
       </c>
       <c r="B307">
@@ -77361,7 +78965,7 @@
       </c>
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A308" s="8" t="s">
+      <c r="A308" t="s">
         <v>1315</v>
       </c>
       <c r="B308">
@@ -77391,7 +78995,7 @@
       </c>
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A309" s="8" t="s">
+      <c r="A309" t="s">
         <v>1316</v>
       </c>
       <c r="B309">
@@ -77421,7 +79025,7 @@
       </c>
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A310" s="8" t="s">
+      <c r="A310" t="s">
         <v>1317</v>
       </c>
       <c r="B310">
@@ -77451,7 +79055,7 @@
       </c>
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A311" s="8" t="s">
+      <c r="A311" t="s">
         <v>1318</v>
       </c>
       <c r="B311">
@@ -77481,7 +79085,7 @@
       </c>
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A312" s="8" t="s">
+      <c r="A312" t="s">
         <v>1319</v>
       </c>
       <c r="B312">
@@ -77511,7 +79115,7 @@
       </c>
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A313" s="8" t="s">
+      <c r="A313" t="s">
         <v>1320</v>
       </c>
       <c r="B313">
@@ -77541,7 +79145,7 @@
       </c>
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A314" s="8" t="s">
+      <c r="A314" t="s">
         <v>1321</v>
       </c>
       <c r="B314">
@@ -77571,7 +79175,7 @@
       </c>
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A315" s="8" t="s">
+      <c r="A315" t="s">
         <v>1322</v>
       </c>
       <c r="B315">
@@ -77601,7 +79205,7 @@
       </c>
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A316" s="8" t="s">
+      <c r="A316" t="s">
         <v>1323</v>
       </c>
       <c r="B316">
@@ -77631,7 +79235,7 @@
       </c>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A317" s="8" t="s">
+      <c r="A317" t="s">
         <v>1324</v>
       </c>
       <c r="B317">
@@ -77661,7 +79265,7 @@
       </c>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A318" s="8" t="s">
+      <c r="A318" t="s">
         <v>1325</v>
       </c>
       <c r="B318">
@@ -77691,7 +79295,7 @@
       </c>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A319" s="8" t="s">
+      <c r="A319" t="s">
         <v>1326</v>
       </c>
       <c r="B319">
@@ -77721,7 +79325,7 @@
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A320" s="8" t="s">
+      <c r="A320" t="s">
         <v>1327</v>
       </c>
       <c r="B320">
@@ -77751,7 +79355,7 @@
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A321" s="8" t="s">
+      <c r="A321" t="s">
         <v>1328</v>
       </c>
       <c r="B321">
@@ -77781,7 +79385,7 @@
       </c>
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A322" s="8" t="s">
+      <c r="A322" t="s">
         <v>1329</v>
       </c>
       <c r="B322">
@@ -77811,7 +79415,7 @@
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A323" s="8" t="s">
+      <c r="A323" t="s">
         <v>1330</v>
       </c>
       <c r="B323">
@@ -77841,7 +79445,7 @@
       </c>
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A324" s="8" t="s">
+      <c r="A324" t="s">
         <v>1331</v>
       </c>
       <c r="B324">
@@ -77871,7 +79475,7 @@
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A325" s="8" t="s">
+      <c r="A325" t="s">
         <v>1332</v>
       </c>
       <c r="B325">
@@ -77901,7 +79505,7 @@
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A326" s="8" t="s">
+      <c r="A326" t="s">
         <v>1333</v>
       </c>
       <c r="B326">
@@ -77931,7 +79535,7 @@
       </c>
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A327" s="8" t="s">
+      <c r="A327" t="s">
         <v>1334</v>
       </c>
       <c r="B327">
@@ -77961,7 +79565,7 @@
       </c>
     </row>
     <row r="328" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A328" s="8" t="s">
+      <c r="A328" t="s">
         <v>1335</v>
       </c>
       <c r="B328">
@@ -77991,7 +79595,7 @@
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A329" s="8" t="s">
+      <c r="A329" t="s">
         <v>1336</v>
       </c>
       <c r="B329">
@@ -78021,7 +79625,7 @@
       </c>
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A330" s="8" t="s">
+      <c r="A330" t="s">
         <v>1337</v>
       </c>
       <c r="B330">
@@ -78051,7 +79655,7 @@
       </c>
     </row>
     <row r="331" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A331" s="8" t="s">
+      <c r="A331" t="s">
         <v>1338</v>
       </c>
       <c r="B331">
@@ -78081,7 +79685,7 @@
       </c>
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A332" s="8" t="s">
+      <c r="A332" t="s">
         <v>1339</v>
       </c>
       <c r="B332">
@@ -78111,7 +79715,7 @@
       </c>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A333" s="8" t="s">
+      <c r="A333" t="s">
         <v>1340</v>
       </c>
       <c r="B333">
@@ -78141,7 +79745,7 @@
       </c>
     </row>
     <row r="334" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A334" s="8" t="s">
+      <c r="A334" t="s">
         <v>1341</v>
       </c>
       <c r="B334">
@@ -78171,7 +79775,7 @@
       </c>
     </row>
     <row r="335" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A335" s="8" t="s">
+      <c r="A335" t="s">
         <v>1342</v>
       </c>
       <c r="B335">
@@ -78201,7 +79805,7 @@
       </c>
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A336" s="8" t="s">
+      <c r="A336" t="s">
         <v>1343</v>
       </c>
       <c r="B336">
@@ -78231,7 +79835,7 @@
       </c>
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A337" s="8" t="s">
+      <c r="A337" t="s">
         <v>1344</v>
       </c>
       <c r="B337">
@@ -78261,7 +79865,7 @@
       </c>
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A338" s="8" t="s">
+      <c r="A338" t="s">
         <v>1345</v>
       </c>
       <c r="B338">
@@ -78291,7 +79895,7 @@
       </c>
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A339" s="8" t="s">
+      <c r="A339" t="s">
         <v>1346</v>
       </c>
       <c r="B339">
@@ -78321,7 +79925,7 @@
       </c>
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A340" s="8" t="s">
+      <c r="A340" t="s">
         <v>1347</v>
       </c>
       <c r="B340">
@@ -78351,7 +79955,7 @@
       </c>
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A341" s="8" t="s">
+      <c r="A341" t="s">
         <v>1348</v>
       </c>
       <c r="B341">
@@ -78381,7 +79985,7 @@
       </c>
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A342" s="8" t="s">
+      <c r="A342" t="s">
         <v>1349</v>
       </c>
       <c r="B342">
@@ -78411,7 +80015,7 @@
       </c>
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A343" s="8" t="s">
+      <c r="A343" t="s">
         <v>1350</v>
       </c>
       <c r="B343">
@@ -78441,7 +80045,7 @@
       </c>
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A344" s="8" t="s">
+      <c r="A344" t="s">
         <v>1351</v>
       </c>
       <c r="B344">
@@ -78471,7 +80075,7 @@
       </c>
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A345" s="8" t="s">
+      <c r="A345" t="s">
         <v>1352</v>
       </c>
       <c r="B345">
@@ -78501,7 +80105,7 @@
       </c>
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A346" s="8" t="s">
+      <c r="A346" t="s">
         <v>1353</v>
       </c>
       <c r="B346">
@@ -78531,7 +80135,7 @@
       </c>
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A347" s="8" t="s">
+      <c r="A347" t="s">
         <v>1354</v>
       </c>
       <c r="B347">
@@ -78561,7 +80165,7 @@
       </c>
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A348" s="8" t="s">
+      <c r="A348" t="s">
         <v>1355</v>
       </c>
       <c r="B348">
@@ -78591,7 +80195,7 @@
       </c>
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A349" s="8" t="s">
+      <c r="A349" t="s">
         <v>1356</v>
       </c>
       <c r="B349">
@@ -78621,7 +80225,7 @@
       </c>
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A350" s="8" t="s">
+      <c r="A350" t="s">
         <v>1357</v>
       </c>
       <c r="B350">
@@ -78651,7 +80255,7 @@
       </c>
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A351" s="8" t="s">
+      <c r="A351" t="s">
         <v>1358</v>
       </c>
       <c r="B351">
@@ -78681,7 +80285,7 @@
       </c>
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A352" s="8" t="s">
+      <c r="A352" t="s">
         <v>1359</v>
       </c>
       <c r="B352">
@@ -78711,7 +80315,7 @@
       </c>
     </row>
     <row r="353" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A353" s="8" t="s">
+      <c r="A353" t="s">
         <v>1360</v>
       </c>
       <c r="B353">
@@ -78741,7 +80345,7 @@
       </c>
     </row>
     <row r="354" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A354" s="8" t="s">
+      <c r="A354" t="s">
         <v>1361</v>
       </c>
       <c r="B354">
@@ -78771,7 +80375,7 @@
       </c>
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A355" s="8" t="s">
+      <c r="A355" t="s">
         <v>1362</v>
       </c>
       <c r="B355">
@@ -78801,7 +80405,7 @@
       </c>
     </row>
     <row r="356" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A356" s="8" t="s">
+      <c r="A356" t="s">
         <v>1363</v>
       </c>
       <c r="B356">
@@ -78831,7 +80435,7 @@
       </c>
     </row>
     <row r="357" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A357" s="8" t="s">
+      <c r="A357" t="s">
         <v>1364</v>
       </c>
       <c r="B357">
@@ -78861,7 +80465,7 @@
       </c>
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A358" s="8" t="s">
+      <c r="A358" t="s">
         <v>1365</v>
       </c>
       <c r="B358">
@@ -78891,7 +80495,7 @@
       </c>
     </row>
     <row r="359" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A359" s="8" t="s">
+      <c r="A359" t="s">
         <v>1366</v>
       </c>
       <c r="B359">
@@ -78921,7 +80525,7 @@
       </c>
     </row>
     <row r="360" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A360" s="8" t="s">
+      <c r="A360" t="s">
         <v>1367</v>
       </c>
       <c r="B360">
@@ -78951,7 +80555,7 @@
       </c>
     </row>
     <row r="361" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A361" s="8" t="s">
+      <c r="A361" t="s">
         <v>1368</v>
       </c>
       <c r="B361">
@@ -78981,7 +80585,7 @@
       </c>
     </row>
     <row r="362" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A362" s="8" t="s">
+      <c r="A362" t="s">
         <v>1369</v>
       </c>
       <c r="B362">
@@ -79011,7 +80615,7 @@
       </c>
     </row>
     <row r="363" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A363" s="8" t="s">
+      <c r="A363" t="s">
         <v>1370</v>
       </c>
       <c r="B363">
@@ -79041,7 +80645,7 @@
       </c>
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A364" s="8" t="s">
+      <c r="A364" t="s">
         <v>1371</v>
       </c>
       <c r="B364">
@@ -79071,7 +80675,7 @@
       </c>
     </row>
     <row r="365" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A365" s="8" t="s">
+      <c r="A365" t="s">
         <v>1372</v>
       </c>
       <c r="B365">
@@ -79101,7 +80705,7 @@
       </c>
     </row>
     <row r="366" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A366" s="8" t="s">
+      <c r="A366" t="s">
         <v>1373</v>
       </c>
       <c r="B366">
@@ -79131,7 +80735,7 @@
       </c>
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A367" s="8" t="s">
+      <c r="A367" t="s">
         <v>1374</v>
       </c>
       <c r="B367">
@@ -79161,7 +80765,7 @@
       </c>
     </row>
     <row r="368" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A368" s="8" t="s">
+      <c r="A368" t="s">
         <v>1375</v>
       </c>
       <c r="B368">
@@ -79191,7 +80795,7 @@
       </c>
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A369" s="8" t="s">
+      <c r="A369" t="s">
         <v>1376</v>
       </c>
       <c r="B369">
@@ -79221,7 +80825,7 @@
       </c>
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A370" s="8" t="s">
+      <c r="A370" t="s">
         <v>1377</v>
       </c>
       <c r="B370">
@@ -79251,7 +80855,7 @@
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A371" s="8" t="s">
+      <c r="A371" t="s">
         <v>1378</v>
       </c>
       <c r="B371">
@@ -79281,7 +80885,7 @@
       </c>
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A372" s="8" t="s">
+      <c r="A372" t="s">
         <v>1379</v>
       </c>
       <c r="B372">
@@ -79311,7 +80915,7 @@
       </c>
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A373" s="8" t="s">
+      <c r="A373" t="s">
         <v>1380</v>
       </c>
       <c r="B373">
@@ -79341,7 +80945,7 @@
       </c>
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A374" s="8" t="s">
+      <c r="A374" t="s">
         <v>1381</v>
       </c>
       <c r="B374">
@@ -79371,7 +80975,7 @@
       </c>
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A375" s="8" t="s">
+      <c r="A375" t="s">
         <v>1382</v>
       </c>
       <c r="B375">
@@ -79401,7 +81005,7 @@
       </c>
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A376" s="8" t="s">
+      <c r="A376" t="s">
         <v>1383</v>
       </c>
       <c r="B376">
@@ -79431,7 +81035,7 @@
       </c>
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A377" s="8" t="s">
+      <c r="A377" t="s">
         <v>1384</v>
       </c>
       <c r="B377">
@@ -79461,7 +81065,7 @@
       </c>
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A378" s="8" t="s">
+      <c r="A378" t="s">
         <v>1385</v>
       </c>
       <c r="B378">
@@ -79491,7 +81095,7 @@
       </c>
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A379" s="8" t="s">
+      <c r="A379" t="s">
         <v>1386</v>
       </c>
       <c r="B379">
@@ -79521,7 +81125,7 @@
       </c>
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A380" s="8" t="s">
+      <c r="A380" t="s">
         <v>1387</v>
       </c>
       <c r="B380">
@@ -79551,7 +81155,7 @@
       </c>
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A381" s="8" t="s">
+      <c r="A381" t="s">
         <v>1388</v>
       </c>
       <c r="B381">
@@ -79581,7 +81185,7 @@
       </c>
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A382" s="8" t="s">
+      <c r="A382" t="s">
         <v>1389</v>
       </c>
       <c r="B382">
@@ -79611,7 +81215,7 @@
       </c>
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A383" s="8" t="s">
+      <c r="A383" t="s">
         <v>1390</v>
       </c>
       <c r="B383">
@@ -79641,7 +81245,7 @@
       </c>
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A384" s="8" t="s">
+      <c r="A384" t="s">
         <v>1391</v>
       </c>
       <c r="B384">
@@ -79671,7 +81275,7 @@
       </c>
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A385" s="8" t="s">
+      <c r="A385" t="s">
         <v>1392</v>
       </c>
       <c r="B385">
@@ -79701,7 +81305,7 @@
       </c>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A386" s="8" t="s">
+      <c r="A386" t="s">
         <v>1393</v>
       </c>
       <c r="B386">
@@ -79731,7 +81335,7 @@
       </c>
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A387" s="8" t="s">
+      <c r="A387" t="s">
         <v>1394</v>
       </c>
       <c r="B387">
@@ -79761,7 +81365,7 @@
       </c>
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A388" s="8" t="s">
+      <c r="A388" t="s">
         <v>1395</v>
       </c>
       <c r="B388">
@@ -79791,7 +81395,7 @@
       </c>
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A389" s="8" t="s">
+      <c r="A389" t="s">
         <v>1396</v>
       </c>
       <c r="B389">
@@ -79821,7 +81425,7 @@
       </c>
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A390" s="8" t="s">
+      <c r="A390" t="s">
         <v>1397</v>
       </c>
       <c r="B390">
@@ -79851,7 +81455,7 @@
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A391" s="8" t="s">
+      <c r="A391" t="s">
         <v>1398</v>
       </c>
       <c r="B391">
@@ -79881,7 +81485,7 @@
       </c>
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A392" s="8" t="s">
+      <c r="A392" t="s">
         <v>1399</v>
       </c>
       <c r="B392">
@@ -79911,7 +81515,7 @@
       </c>
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A393" s="8" t="s">
+      <c r="A393" t="s">
         <v>1400</v>
       </c>
       <c r="B393">
@@ -79941,7 +81545,7 @@
       </c>
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A394" s="8" t="s">
+      <c r="A394" t="s">
         <v>1401</v>
       </c>
       <c r="B394">
@@ -79971,7 +81575,7 @@
       </c>
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A395" s="8" t="s">
+      <c r="A395" t="s">
         <v>1402</v>
       </c>
       <c r="B395">
@@ -80001,7 +81605,7 @@
       </c>
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A396" s="8" t="s">
+      <c r="A396" t="s">
         <v>1403</v>
       </c>
       <c r="B396">
@@ -80031,7 +81635,7 @@
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A397" s="8" t="s">
+      <c r="A397" t="s">
         <v>1404</v>
       </c>
       <c r="B397">
@@ -80061,7 +81665,7 @@
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A398" s="8" t="s">
+      <c r="A398" t="s">
         <v>1405</v>
       </c>
       <c r="B398">
@@ -80091,7 +81695,7 @@
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A399" s="8" t="s">
+      <c r="A399" t="s">
         <v>1406</v>
       </c>
       <c r="B399">
@@ -80121,7 +81725,7 @@
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A400" s="8" t="s">
+      <c r="A400" t="s">
         <v>1407</v>
       </c>
       <c r="B400">
@@ -80151,7 +81755,7 @@
       </c>
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A401" s="8" t="s">
+      <c r="A401" t="s">
         <v>1408</v>
       </c>
       <c r="B401">
@@ -80181,7 +81785,7 @@
       </c>
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A402" s="8" t="s">
+      <c r="A402" t="s">
         <v>1409</v>
       </c>
       <c r="B402">
@@ -80211,7 +81815,7 @@
       </c>
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A403" s="8" t="s">
+      <c r="A403" t="s">
         <v>1410</v>
       </c>
       <c r="B403">
@@ -80241,7 +81845,7 @@
       </c>
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A404" s="8" t="s">
+      <c r="A404" t="s">
         <v>1411</v>
       </c>
       <c r="B404">
@@ -80271,7 +81875,7 @@
       </c>
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A405" s="8" t="s">
+      <c r="A405" t="s">
         <v>1412</v>
       </c>
       <c r="B405">
@@ -80301,7 +81905,7 @@
       </c>
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A406" s="8" t="s">
+      <c r="A406" t="s">
         <v>1413</v>
       </c>
       <c r="B406">
@@ -80331,7 +81935,7 @@
       </c>
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A407" s="8" t="s">
+      <c r="A407" t="s">
         <v>1414</v>
       </c>
       <c r="B407">
@@ -80361,7 +81965,7 @@
       </c>
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A408" s="8" t="s">
+      <c r="A408" t="s">
         <v>1415</v>
       </c>
       <c r="B408">
@@ -80391,7 +81995,7 @@
       </c>
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A409" s="8" t="s">
+      <c r="A409" t="s">
         <v>1416</v>
       </c>
       <c r="B409">
@@ -80421,7 +82025,7 @@
       </c>
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A410" s="8" t="s">
+      <c r="A410" t="s">
         <v>1417</v>
       </c>
       <c r="B410">
@@ -80451,7 +82055,7 @@
       </c>
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A411" s="8" t="s">
+      <c r="A411" t="s">
         <v>1418</v>
       </c>
       <c r="B411">
@@ -80481,7 +82085,7 @@
       </c>
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A412" s="8" t="s">
+      <c r="A412" t="s">
         <v>1419</v>
       </c>
       <c r="B412">
@@ -80511,7 +82115,7 @@
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A413" s="8" t="s">
+      <c r="A413" t="s">
         <v>1420</v>
       </c>
       <c r="B413">
@@ -80541,7 +82145,7 @@
       </c>
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A414" s="8" t="s">
+      <c r="A414" t="s">
         <v>1421</v>
       </c>
       <c r="B414">
@@ -80571,7 +82175,7 @@
       </c>
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A415" s="8" t="s">
+      <c r="A415" t="s">
         <v>1422</v>
       </c>
       <c r="B415">
@@ -80601,7 +82205,7 @@
       </c>
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A416" s="8" t="s">
+      <c r="A416" t="s">
         <v>1423</v>
       </c>
       <c r="B416">
@@ -80631,7 +82235,7 @@
       </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A417" s="8" t="s">
+      <c r="A417" t="s">
         <v>1424</v>
       </c>
       <c r="B417">
@@ -80661,7 +82265,7 @@
       </c>
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A418" s="8" t="s">
+      <c r="A418" t="s">
         <v>1425</v>
       </c>
       <c r="B418">
@@ -80691,7 +82295,7 @@
       </c>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A419" s="8" t="s">
+      <c r="A419" t="s">
         <v>1426</v>
       </c>
       <c r="B419">
@@ -80721,7 +82325,7 @@
       </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A420" s="8" t="s">
+      <c r="A420" t="s">
         <v>1427</v>
       </c>
       <c r="B420">
@@ -80751,7 +82355,7 @@
       </c>
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A421" s="8" t="s">
+      <c r="A421" t="s">
         <v>1428</v>
       </c>
       <c r="B421">
@@ -80781,7 +82385,7 @@
       </c>
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A422" s="8" t="s">
+      <c r="A422" t="s">
         <v>1429</v>
       </c>
       <c r="B422">
@@ -80811,7 +82415,7 @@
       </c>
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A423" s="8" t="s">
+      <c r="A423" t="s">
         <v>1430</v>
       </c>
       <c r="B423">
@@ -80841,7 +82445,7 @@
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A424" s="8" t="s">
+      <c r="A424" t="s">
         <v>1431</v>
       </c>
       <c r="B424">
@@ -80871,7 +82475,7 @@
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A425" s="8" t="s">
+      <c r="A425" t="s">
         <v>1432</v>
       </c>
       <c r="B425">
@@ -80901,7 +82505,7 @@
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A426" s="8" t="s">
+      <c r="A426" t="s">
         <v>1433</v>
       </c>
       <c r="B426">
@@ -80931,7 +82535,7 @@
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A427" s="8" t="s">
+      <c r="A427" t="s">
         <v>1434</v>
       </c>
       <c r="B427">
@@ -80961,7 +82565,7 @@
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A428" s="8" t="s">
+      <c r="A428" t="s">
         <v>1435</v>
       </c>
       <c r="B428">
@@ -80991,7 +82595,7 @@
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A429" s="8" t="s">
+      <c r="A429" t="s">
         <v>1436</v>
       </c>
       <c r="B429">
@@ -81021,7 +82625,7 @@
       </c>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A430" s="8" t="s">
+      <c r="A430" t="s">
         <v>1437</v>
       </c>
       <c r="B430">
@@ -81051,7 +82655,7 @@
       </c>
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A431" s="8" t="s">
+      <c r="A431" t="s">
         <v>1438</v>
       </c>
       <c r="B431">
@@ -81081,7 +82685,7 @@
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A432" s="8" t="s">
+      <c r="A432" t="s">
         <v>1439</v>
       </c>
       <c r="B432">
@@ -81111,7 +82715,7 @@
       </c>
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A433" s="8" t="s">
+      <c r="A433" t="s">
         <v>1440</v>
       </c>
       <c r="B433">
@@ -81141,7 +82745,7 @@
       </c>
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A434" s="8" t="s">
+      <c r="A434" t="s">
         <v>1441</v>
       </c>
       <c r="B434">
@@ -81171,7 +82775,7 @@
       </c>
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A435" s="8" t="s">
+      <c r="A435" t="s">
         <v>1442</v>
       </c>
       <c r="B435">
@@ -81201,7 +82805,7 @@
       </c>
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A436" s="8" t="s">
+      <c r="A436" t="s">
         <v>1443</v>
       </c>
       <c r="B436">
@@ -81231,7 +82835,7 @@
       </c>
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A437" s="8" t="s">
+      <c r="A437" t="s">
         <v>1444</v>
       </c>
       <c r="B437">
@@ -81261,7 +82865,7 @@
       </c>
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A438" s="8" t="s">
+      <c r="A438" t="s">
         <v>1445</v>
       </c>
       <c r="B438">
@@ -81291,7 +82895,7 @@
       </c>
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A439" s="8" t="s">
+      <c r="A439" t="s">
         <v>1446</v>
       </c>
       <c r="B439">
@@ -81321,7 +82925,7 @@
       </c>
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A440" s="8" t="s">
+      <c r="A440" t="s">
         <v>1447</v>
       </c>
       <c r="B440">
@@ -81351,7 +82955,7 @@
       </c>
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A441" s="8" t="s">
+      <c r="A441" t="s">
         <v>1448</v>
       </c>
       <c r="B441">
@@ -81381,7 +82985,7 @@
       </c>
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A442" s="8" t="s">
+      <c r="A442" t="s">
         <v>1449</v>
       </c>
       <c r="B442">
@@ -81411,7 +83015,7 @@
       </c>
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A443" s="8" t="s">
+      <c r="A443" t="s">
         <v>1450</v>
       </c>
       <c r="B443">
@@ -81441,7 +83045,7 @@
       </c>
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A444" s="8" t="s">
+      <c r="A444" t="s">
         <v>1451</v>
       </c>
       <c r="B444">
@@ -81471,7 +83075,7 @@
       </c>
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A445" s="8" t="s">
+      <c r="A445" t="s">
         <v>1452</v>
       </c>
       <c r="B445">
@@ -81501,7 +83105,7 @@
       </c>
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A446" s="8" t="s">
+      <c r="A446" t="s">
         <v>1453</v>
       </c>
       <c r="B446">
@@ -81531,7 +83135,7 @@
       </c>
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A447" s="8" t="s">
+      <c r="A447" t="s">
         <v>1454</v>
       </c>
       <c r="B447">
@@ -81561,7 +83165,7 @@
       </c>
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A448" s="8" t="s">
+      <c r="A448" t="s">
         <v>1455</v>
       </c>
       <c r="B448">
@@ -81591,7 +83195,7 @@
       </c>
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A449" s="8" t="s">
+      <c r="A449" t="s">
         <v>1456</v>
       </c>
       <c r="B449">
@@ -81621,7 +83225,7 @@
       </c>
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A450" s="8" t="s">
+      <c r="A450" t="s">
         <v>1457</v>
       </c>
       <c r="B450">
@@ -81651,7 +83255,7 @@
       </c>
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A451" s="8" t="s">
+      <c r="A451" t="s">
         <v>1458</v>
       </c>
       <c r="B451">
@@ -81681,7 +83285,7 @@
       </c>
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A452" s="8" t="s">
+      <c r="A452" t="s">
         <v>1459</v>
       </c>
       <c r="B452">
@@ -81711,7 +83315,7 @@
       </c>
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A453" s="8" t="s">
+      <c r="A453" t="s">
         <v>1460</v>
       </c>
       <c r="B453">
@@ -81741,7 +83345,7 @@
       </c>
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A454" s="8" t="s">
+      <c r="A454" t="s">
         <v>1461</v>
       </c>
       <c r="B454">
@@ -81771,7 +83375,7 @@
       </c>
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A455" s="8" t="s">
+      <c r="A455" t="s">
         <v>1462</v>
       </c>
       <c r="B455">
@@ -81801,7 +83405,7 @@
       </c>
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A456" s="8" t="s">
+      <c r="A456" t="s">
         <v>1463</v>
       </c>
       <c r="B456">
@@ -81831,7 +83435,7 @@
       </c>
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A457" s="8" t="s">
+      <c r="A457" t="s">
         <v>1464</v>
       </c>
       <c r="B457">
@@ -81861,7 +83465,7 @@
       </c>
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A458" s="8" t="s">
+      <c r="A458" t="s">
         <v>1465</v>
       </c>
       <c r="B458">
@@ -81891,7 +83495,7 @@
       </c>
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A459" s="8" t="s">
+      <c r="A459" t="s">
         <v>1466</v>
       </c>
       <c r="B459">
@@ -81921,7 +83525,7 @@
       </c>
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A460" s="8" t="s">
+      <c r="A460" t="s">
         <v>1467</v>
       </c>
       <c r="B460">
@@ -81951,7 +83555,7 @@
       </c>
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A461" s="8" t="s">
+      <c r="A461" t="s">
         <v>1468</v>
       </c>
       <c r="B461">
@@ -81981,7 +83585,7 @@
       </c>
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A462" s="8" t="s">
+      <c r="A462" t="s">
         <v>1469</v>
       </c>
       <c r="B462">
@@ -82011,7 +83615,7 @@
       </c>
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A463" s="8" t="s">
+      <c r="A463" t="s">
         <v>1470</v>
       </c>
       <c r="B463">
@@ -82041,7 +83645,7 @@
       </c>
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A464" s="8" t="s">
+      <c r="A464" t="s">
         <v>1471</v>
       </c>
       <c r="B464">
@@ -82071,7 +83675,7 @@
       </c>
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A465" s="8" t="s">
+      <c r="A465" t="s">
         <v>1472</v>
       </c>
       <c r="B465">
@@ -82101,7 +83705,7 @@
       </c>
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A466" s="8" t="s">
+      <c r="A466" t="s">
         <v>1473</v>
       </c>
       <c r="B466">
@@ -82131,7 +83735,7 @@
       </c>
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A467" s="8" t="s">
+      <c r="A467" t="s">
         <v>1474</v>
       </c>
       <c r="B467">
@@ -82161,7 +83765,7 @@
       </c>
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A468" s="8" t="s">
+      <c r="A468" t="s">
         <v>1475</v>
       </c>
       <c r="B468">
@@ -82191,7 +83795,7 @@
       </c>
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A469" s="8" t="s">
+      <c r="A469" t="s">
         <v>1476</v>
       </c>
       <c r="B469">
@@ -82221,7 +83825,7 @@
       </c>
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A470" s="8" t="s">
+      <c r="A470" t="s">
         <v>1477</v>
       </c>
       <c r="B470">
@@ -82251,7 +83855,7 @@
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A471" s="8" t="s">
+      <c r="A471" t="s">
         <v>1478</v>
       </c>
       <c r="B471">
@@ -82281,7 +83885,7 @@
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A472" s="8" t="s">
+      <c r="A472" t="s">
         <v>1479</v>
       </c>
       <c r="B472">
@@ -82311,7 +83915,7 @@
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A473" s="8" t="s">
+      <c r="A473" t="s">
         <v>1480</v>
       </c>
       <c r="B473">
@@ -82341,7 +83945,7 @@
       </c>
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A474" s="8" t="s">
+      <c r="A474" t="s">
         <v>1481</v>
       </c>
       <c r="B474">
@@ -82371,7 +83975,7 @@
       </c>
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A475" s="8" t="s">
+      <c r="A475" t="s">
         <v>1482</v>
       </c>
       <c r="B475">
@@ -82401,7 +84005,7 @@
       </c>
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A476" s="8" t="s">
+      <c r="A476" t="s">
         <v>1483</v>
       </c>
       <c r="B476">
@@ -82431,7 +84035,7 @@
       </c>
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A477" s="8" t="s">
+      <c r="A477" t="s">
         <v>1484</v>
       </c>
       <c r="B477">
@@ -82461,7 +84065,7 @@
       </c>
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A478" s="8" t="s">
+      <c r="A478" t="s">
         <v>1485</v>
       </c>
       <c r="B478">
@@ -82491,7 +84095,7 @@
       </c>
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A479" s="8" t="s">
+      <c r="A479" t="s">
         <v>1486</v>
       </c>
       <c r="B479">
@@ -82521,7 +84125,7 @@
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A480" s="8" t="s">
+      <c r="A480" t="s">
         <v>1487</v>
       </c>
       <c r="B480">
@@ -82551,7 +84155,7 @@
       </c>
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A481" s="8" t="s">
+      <c r="A481" t="s">
         <v>1488</v>
       </c>
       <c r="B481">
@@ -82581,7 +84185,7 @@
       </c>
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A482" s="8" t="s">
+      <c r="A482" t="s">
         <v>1489</v>
       </c>
       <c r="B482">
@@ -82611,7 +84215,7 @@
       </c>
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A483" s="8" t="s">
+      <c r="A483" t="s">
         <v>1490</v>
       </c>
       <c r="B483">
@@ -82641,7 +84245,7 @@
       </c>
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A484" s="8" t="s">
+      <c r="A484" t="s">
         <v>1491</v>
       </c>
       <c r="B484">
@@ -82671,7 +84275,7 @@
       </c>
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A485" s="8" t="s">
+      <c r="A485" t="s">
         <v>1492</v>
       </c>
       <c r="B485">
@@ -82701,7 +84305,7 @@
       </c>
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A486" s="8" t="s">
+      <c r="A486" t="s">
         <v>1493</v>
       </c>
       <c r="B486">
@@ -82731,7 +84335,7 @@
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A487" s="8" t="s">
+      <c r="A487" t="s">
         <v>1494</v>
       </c>
       <c r="B487">
@@ -82761,7 +84365,7 @@
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A488" s="8" t="s">
+      <c r="A488" t="s">
         <v>1495</v>
       </c>
       <c r="B488">
@@ -82791,7 +84395,7 @@
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A489" s="8" t="s">
+      <c r="A489" t="s">
         <v>1496</v>
       </c>
       <c r="B489">
@@ -82821,7 +84425,7 @@
       </c>
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A490" s="8" t="s">
+      <c r="A490" t="s">
         <v>1497</v>
       </c>
       <c r="B490">
@@ -82851,7 +84455,7 @@
       </c>
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A491" s="8" t="s">
+      <c r="A491" t="s">
         <v>1498</v>
       </c>
       <c r="B491">
@@ -82881,7 +84485,7 @@
       </c>
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A492" s="8" t="s">
+      <c r="A492" t="s">
         <v>1499</v>
       </c>
       <c r="B492">
@@ -82911,7 +84515,7 @@
       </c>
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A493" s="8" t="s">
+      <c r="A493" t="s">
         <v>1500</v>
       </c>
       <c r="B493">
@@ -82941,7 +84545,7 @@
       </c>
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A494" s="8" t="s">
+      <c r="A494" t="s">
         <v>1501</v>
       </c>
       <c r="B494">
@@ -82971,7 +84575,7 @@
       </c>
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A495" s="8" t="s">
+      <c r="A495" t="s">
         <v>1502</v>
       </c>
       <c r="B495">
@@ -83001,7 +84605,7 @@
       </c>
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A496" s="8" t="s">
+      <c r="A496" t="s">
         <v>1503</v>
       </c>
       <c r="B496">
@@ -83031,7 +84635,7 @@
       </c>
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A497" s="8" t="s">
+      <c r="A497" t="s">
         <v>1504</v>
       </c>
       <c r="B497">
@@ -83061,7 +84665,7 @@
       </c>
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A498" s="8" t="s">
+      <c r="A498" t="s">
         <v>1505</v>
       </c>
       <c r="B498">
@@ -83091,7 +84695,7 @@
       </c>
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A499" s="8" t="s">
+      <c r="A499" t="s">
         <v>1506</v>
       </c>
       <c r="B499">
@@ -83121,7 +84725,7 @@
       </c>
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A500" s="8" t="s">
+      <c r="A500" t="s">
         <v>1507</v>
       </c>
       <c r="B500">
@@ -83151,7 +84755,7 @@
       </c>
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A501" s="8" t="s">
+      <c r="A501" t="s">
         <v>1508</v>
       </c>
       <c r="B501">
@@ -83181,7 +84785,7 @@
       </c>
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A502" s="8" t="s">
+      <c r="A502" t="s">
         <v>1509</v>
       </c>
       <c r="B502">
@@ -83217,182 +84821,6 @@
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA538C55-3497-42D2-A195-3A2123A31A61}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1990</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2005</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2006</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2007</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2008</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <f>SUM(Orders!J2:J1001)</f>
-        <v>594986</v>
-      </c>
-      <c r="B2">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="2">
-        <f>A2/B2</f>
-        <v>594.98599999999999</v>
-      </c>
-      <c r="D2">
-        <f>COUNTA(_xlfn.UNIQUE(Orders!C2:C1001))</f>
-        <v>501</v>
-      </c>
-      <c r="E2">
-        <f>COUNTIF(Orders!K2:K1001,"&gt;1")</f>
-        <v>499</v>
-      </c>
-      <c r="F2" s="3">
-        <f>E2/D2*100</f>
-        <v>99.600798403193608</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2012</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>2014</v>
-      </c>
-      <c r="E5" t="s">
-        <v>2012</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>2015</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B6">
-        <v>30008</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E6">
-        <v>312714</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>1995</v>
-      </c>
-      <c r="H6">
-        <v>141154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B7">
-        <v>359997</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>1994</v>
-      </c>
-      <c r="E7">
-        <v>282272</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>1998</v>
-      </c>
-      <c r="H7">
-        <v>114051</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B8">
-        <v>204981</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>2011</v>
-      </c>
-      <c r="E8">
-        <v>594986</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>1993</v>
-      </c>
-      <c r="H8">
-        <v>104792</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>2011</v>
-      </c>
-      <c r="B9">
-        <v>594986</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>2001</v>
-      </c>
-      <c r="H9">
-        <v>74774</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G10" s="5" t="s">
-        <v>2004</v>
-      </c>
-      <c r="H10">
-        <v>70291</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G11" s="5" t="s">
-        <v>2011</v>
-      </c>
-      <c r="H11">
-        <v>505062</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
